--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA679F9-04DE-4807-AA8B-41A8C8DBCA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CBD4CC-109E-4B0A-8AAC-D6DAF2A885EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="116">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -67,57 +67,9 @@
     <t>Student 2:</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
     <t>Student 3:</t>
   </si>
   <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F02.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> cautarea filmelor care au un anumit regizor (sau parti din numele regizorului);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">F02. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cautarea filmelor care au un anumit regizor (sau parti din numele regizorului).</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">F02. Covered source code </t>
   </si>
   <si>
@@ -211,21 +163,6 @@
     <t>Loop (lc)</t>
   </si>
   <si>
-    <t>F02_Cond01 &gt; 100</t>
-  </si>
-  <si>
-    <t>F02_Cond02 &lt; 20</t>
-  </si>
-  <si>
-    <t>F02_Cond03 == i</t>
-  </si>
-  <si>
-    <t>F02_Condnn &lt; n</t>
-  </si>
-  <si>
-    <t>F02_Pnn</t>
-  </si>
-  <si>
     <t>n-1</t>
   </si>
   <si>
@@ -250,9 +187,6 @@
     <t>1, 2,4, 6, 7</t>
   </si>
   <si>
-    <t>F01_TC02</t>
-  </si>
-  <si>
     <t>WBT Implemented TCs</t>
   </si>
   <si>
@@ -290,9 +224,6 @@
   </si>
   <si>
     <t>Depanare</t>
-  </si>
-  <si>
-    <t>Re-testare</t>
   </si>
   <si>
     <t>Testare de regresie</t>
@@ -360,44 +291,6 @@
         <family val="2"/>
       </rPr>
       <t>[se va indica numarul de bug-uri identificate prin depanare, la nivelul metodei testate]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#Bugs Fixed </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="8"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>[se va completa cu 'da' dupa depanare]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Re-testare </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>[se va completa cu 'da' dupa retestare]</t>
     </r>
   </si>
   <si>
@@ -484,9 +377,6 @@
     </r>
   </si>
   <si>
-    <t>nu</t>
-  </si>
-  <si>
     <t>F02_P04</t>
   </si>
   <si>
@@ -528,12 +418,132 @@
       <t>Consuma Stoc</t>
     </r>
   </si>
+  <si>
+    <t>F02. consuma, cat se consuma din stoc si verificare</t>
+  </si>
+  <si>
+    <t>Cafea: stoc 10.0, necesar 2.0</t>
+  </si>
+  <si>
+    <t>Stoc actualizat: 8.0</t>
+  </si>
+  <si>
+    <t>Sirop: stoc 1.5, necesar 1.5</t>
+  </si>
+  <si>
+    <t>Stoc actualizat: 0.0</t>
+  </si>
+  <si>
+    <t>F02_TC03</t>
+  </si>
+  <si>
+    <t>F02_TC04</t>
+  </si>
+  <si>
+    <t>Lapte: stoc 1.0, necesar 3.0</t>
+  </si>
+  <si>
+    <t>Miere: stoc 0.0, necesar 1.0</t>
+  </si>
+  <si>
+    <t>IllegalStateException</t>
+  </si>
+  <si>
+    <t>1,3,4,5,6,7</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>F02_eroare</t>
+  </si>
+  <si>
+    <t>F02_succes</t>
+  </si>
+  <si>
+    <t>Cafea</t>
+  </si>
+  <si>
+    <t>Sirop</t>
+  </si>
+  <si>
+    <t>Lapte</t>
+  </si>
+  <si>
+    <t>Miere</t>
+  </si>
+  <si>
+    <t>Stoc: 10, Cerut: 2</t>
+  </si>
+  <si>
+    <t>Stoc: 1.5, Cerut: 1.5</t>
+  </si>
+  <si>
+    <t>Stoc: 1, Cerut: 3</t>
+  </si>
+  <si>
+    <t>Stoc: 0, Cerut: 1</t>
+  </si>
+  <si>
+    <t>Stoc nou: 8.0</t>
+  </si>
+  <si>
+    <t>Stoc nou: 0.0</t>
+  </si>
+  <si>
+    <t>Passed (Exception)</t>
+  </si>
+  <si>
+    <t>Passed (8.0)</t>
+  </si>
+  <si>
+    <t>…Passed (0.0)</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>Porcar Cezar</t>
+  </si>
+  <si>
+    <t>Potra-Ratiu Darisu</t>
+  </si>
+  <si>
+    <t>1. Consuma stoc</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>F02.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Consuma stocul din magazin</t>
+    </r>
+  </si>
+  <si>
+    <t>Un magazin doreste sa modifice vazand anumite produse functionalitate permisa este:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,13 +587,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,13 +613,6 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -749,7 +745,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -808,21 +804,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -1100,19 +1081,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -1212,298 +1180,275 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1907,26 +1852,26 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="66" t="s">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="68"/>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="73"/>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1936,88 +1881,96 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29" t="s">
+      <c r="N6" s="26"/>
+      <c r="O6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="29" t="s">
+      <c r="P6" s="26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O7" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="P7" s="26">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="29" t="s">
+      <c r="N8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O8" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="P8" s="26">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N9" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="39" t="s">
-        <v>14</v>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
     </row>
   </sheetData>
@@ -2035,361 +1988,361 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:T24"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="41.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="20" max="20" width="41.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="66" t="s">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="87" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="89"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="66" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="73"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B3" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="79"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="I6" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="Q6" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B8" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="I6" s="66" t="s">
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="I8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="Q6" s="66" t="s">
+      <c r="Q8" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="34" t="s">
+      <c r="R8" s="76"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="I8" s="12" t="s">
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="I9" s="36"/>
+      <c r="Q9" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="86" t="s">
+      <c r="R9" s="76"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B10" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="86"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="36">
+      <c r="C10" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="I10" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="82"/>
+      <c r="Q10" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="76"/>
+      <c r="T10" s="32">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="I9" s="40"/>
-      <c r="Q9" s="86" t="s">
-        <v>25</v>
-      </c>
-      <c r="R9" s="86"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B11" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="I10" s="90" t="s">
+      <c r="C11" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="85"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B12" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="92"/>
-      <c r="Q10" s="86" t="s">
+      <c r="C12" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="85"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B13" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="R10" s="86" t="s">
+      <c r="C13" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="85"/>
+      <c r="Q13" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="S10" s="86"/>
-      <c r="T10" s="36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B11" s="37" t="s">
+      <c r="R13" s="61"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="61"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B14" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="85"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I15" s="83"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="85"/>
+      <c r="Q15" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="95"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
+      <c r="R15" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="95"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B13" s="37" t="s">
+      <c r="S15" s="89"/>
+      <c r="T15" s="89"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I16" s="83"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="85"/>
+      <c r="Q16" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="95"/>
-      <c r="Q13" s="66" t="s">
+      <c r="R16" s="74" t="s">
+        <v>76</v>
+      </c>
+      <c r="S16" s="74"/>
+      <c r="T16" s="74"/>
+    </row>
+    <row r="17" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I17" s="83"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="85"/>
+      <c r="Q17" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="R13" s="67"/>
-      <c r="S13" s="67"/>
-      <c r="T13" s="67"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B14" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="94"/>
-      <c r="O14" s="95"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="I15" s="93"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="94"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="94"/>
-      <c r="O15" s="95"/>
-      <c r="Q15" s="34" t="s">
+      <c r="R17" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="S17" s="74"/>
+      <c r="T17" s="74"/>
+    </row>
+    <row r="18" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I18" s="83"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="85"/>
+      <c r="Q18" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="R15" s="99" t="s">
-        <v>35</v>
-      </c>
-      <c r="S15" s="99"/>
-      <c r="T15" s="99"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="I16" s="93"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="94"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="94"/>
-      <c r="O16" s="95"/>
-      <c r="Q16" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="R16" s="84" t="s">
-        <v>90</v>
-      </c>
-      <c r="S16" s="84"/>
-      <c r="T16" s="84"/>
-    </row>
-    <row r="17" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I17" s="93"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="95"/>
-      <c r="Q17" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="R17" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="S17" s="84"/>
-      <c r="T17" s="84"/>
-    </row>
-    <row r="18" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I18" s="93"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="94"/>
-      <c r="O18" s="95"/>
-      <c r="Q18" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="R18" s="84" t="s">
-        <v>92</v>
-      </c>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-    </row>
-    <row r="19" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I19" s="93"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="95"/>
-      <c r="Q19" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="R19" s="84" t="s">
-        <v>93</v>
-      </c>
-      <c r="S19" s="84"/>
-      <c r="T19" s="84"/>
-    </row>
-    <row r="20" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I20" s="93"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="95"/>
-      <c r="Q20" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="R20" s="84" t="s">
-        <v>94</v>
-      </c>
-      <c r="S20" s="84"/>
-      <c r="T20" s="84"/>
-    </row>
-    <row r="21" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I21" s="93"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="95"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-    </row>
-    <row r="22" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I22" s="93"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="95"/>
-    </row>
-    <row r="23" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I23" s="93"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
-      <c r="O23" s="95"/>
-    </row>
-    <row r="24" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="97"/>
-      <c r="M24" s="97"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="98"/>
+      <c r="R18" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="S18" s="74"/>
+      <c r="T18" s="74"/>
+    </row>
+    <row r="19" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I19" s="83"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="85"/>
+      <c r="Q19" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="R19" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="S19" s="74"/>
+      <c r="T19" s="74"/>
+    </row>
+    <row r="20" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="85"/>
+      <c r="Q20" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="R20" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="S20" s="74"/>
+      <c r="T20" s="74"/>
+    </row>
+    <row r="21" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I21" s="83"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="85"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="74"/>
+      <c r="S21" s="74"/>
+      <c r="T21" s="74"/>
+    </row>
+    <row r="22" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I22" s="83"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="85"/>
+    </row>
+    <row r="23" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I23" s="83"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="85"/>
+    </row>
+    <row r="24" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I24" s="86"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="87"/>
+      <c r="O24" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2418,7 +2371,7 @@
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="C14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2430,474 +2383,381 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:AB16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:R16"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
-    <col min="16" max="17" width="8.85546875" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
-    <col min="22" max="24" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="10" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="14" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="66" t="s">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="68"/>
-    </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B3" s="87" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
-    </row>
-    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
-    </row>
-    <row r="6" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="106" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="73"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="96" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="79"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="97" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="97" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="97" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="97"/>
+      <c r="R6" s="97"/>
+    </row>
+    <row r="7" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="97"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="106" t="s">
+      <c r="F7" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="107" t="s">
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="106" t="s">
+      <c r="K7" s="94"/>
+      <c r="L7" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="106"/>
-      <c r="Q6" s="106"/>
-      <c r="R6" s="106"/>
-      <c r="S6" s="106"/>
-      <c r="T6" s="106"/>
-      <c r="U6" s="106"/>
-      <c r="V6" s="106"/>
-      <c r="W6" s="106"/>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="106"/>
-      <c r="Z6" s="106"/>
-      <c r="AA6" s="106"/>
-      <c r="AB6" s="106"/>
-    </row>
-    <row r="7" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="103" t="s">
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+    </row>
+    <row r="8" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="97"/>
+      <c r="C8" s="90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="92"/>
+      <c r="F8" s="93" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="93"/>
+      <c r="J8" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="94" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="95">
+        <v>0</v>
+      </c>
+      <c r="M8" s="95">
+        <v>1</v>
+      </c>
+      <c r="N8" s="95">
+        <v>2</v>
+      </c>
+      <c r="O8" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="102" t="s">
+      <c r="P8" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="104" t="s">
+      <c r="Q8" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="104"/>
-      <c r="S7" s="104"/>
-      <c r="T7" s="104"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="105" t="s">
+      <c r="R8" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="W7" s="105"/>
-      <c r="X7" s="105"/>
-      <c r="Y7" s="105"/>
-      <c r="Z7" s="105"/>
-      <c r="AA7" s="105"/>
-      <c r="AB7" s="105"/>
-    </row>
-    <row r="8" spans="2:28" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="106"/>
-      <c r="C8" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="103"/>
-      <c r="F8" s="102" t="s">
+    </row>
+    <row r="9" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="97"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102" t="s">
+      <c r="G9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102" t="s">
+      <c r="H9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="95"/>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
+    </row>
+    <row r="10" spans="2:18" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102" t="s">
+      <c r="C10" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="O8" s="102"/>
-      <c r="P8" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="104" t="s">
-        <v>37</v>
-      </c>
-      <c r="R8" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="S8" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="T8" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="U8" s="104" t="s">
-        <v>51</v>
-      </c>
-      <c r="V8" s="105">
-        <v>0</v>
-      </c>
-      <c r="W8" s="105">
-        <v>1</v>
-      </c>
-      <c r="X8" s="105">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="105" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z8" s="105" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA8" s="105" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB8" s="105" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="106"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="104"/>
-      <c r="S9" s="104"/>
-      <c r="T9" s="104"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
-      <c r="AA9" s="105"/>
-      <c r="AB9" s="105"/>
-    </row>
-    <row r="10" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
+      <c r="M10" s="17" t="s">
+        <v>94</v>
+      </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-    </row>
-    <row r="11" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+    </row>
+    <row r="11" spans="2:18" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
+      <c r="C11" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+      <c r="M11" s="17" t="s">
+        <v>94</v>
+      </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-    </row>
-    <row r="12" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+    </row>
+    <row r="12" spans="2:18" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="17" t="s">
+        <v>94</v>
+      </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-    </row>
-    <row r="13" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+    </row>
+    <row r="13" spans="2:18" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B13" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="17" t="s">
+        <v>94</v>
+      </c>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-    </row>
-    <row r="14" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+    </row>
+    <row r="14" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-    </row>
-    <row r="15" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+    </row>
+    <row r="15" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-    </row>
-    <row r="16" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="22"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+    </row>
+    <row r="16" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="23">
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:AB6"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E6:R6"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="L7:R7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="R8:R9"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:U7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2909,254 +2769,182 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:N16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:J16"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="66" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="68"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="72" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="73"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="71"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="81"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="69"/>
+      <c r="G4" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="66"/>
+    </row>
+    <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="64"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="72"/>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="75"/>
-      <c r="K5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="23">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="21">
         <v>9</v>
       </c>
-      <c r="C6" s="76" t="s">
-        <v>69</v>
+      <c r="C6" s="67" t="s">
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="83"/>
-      <c r="K6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="23">
+        <v>49</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="21">
         <v>10</v>
       </c>
-      <c r="C7" s="76"/>
+      <c r="C7" s="67"/>
       <c r="D7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="23">
-        <v>5</v>
-      </c>
-      <c r="F7" s="23">
-        <v>6</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="73"/>
-      <c r="K7" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="23">
+        <v>60</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="21">
         <v>11</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="73"/>
-      <c r="K8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="23">
+      <c r="C8" s="67"/>
+      <c r="D8" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="21">
         <v>12</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="73"/>
-      <c r="K9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="67"/>
+      <c r="D9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="9" t="s">
-        <v>23</v>
+      <c r="C10" s="68"/>
+      <c r="D10" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="75"/>
-      <c r="K10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -3164,167 +2952,122 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="41"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="48"/>
+    </row>
+    <row r="14" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="K12" s="25"/>
-    </row>
-    <row r="13" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="58" t="s">
+      <c r="I14" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="50" t="s">
+      <c r="J14" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="51"/>
-      <c r="H13" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" s="65"/>
-    </row>
-    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="L14" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="M14" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="N14" s="53" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="43"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="48"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="29">
-        <f>SUM(C16:D16)</f>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="49"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="54"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="26">
+        <v>4</v>
+      </c>
+      <c r="C16" s="24">
+        <v>4</v>
+      </c>
+      <c r="D16" s="24">
         <v>0</v>
       </c>
-      <c r="C16" s="26">
+      <c r="E16" s="39">
+        <v>1</v>
+      </c>
+      <c r="F16" s="25">
         <v>0</v>
       </c>
-      <c r="D16" s="26">
+      <c r="G16" s="27">
         <v>0</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="29">
-        <f>SUM(J16:K16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="26">
-        <v>0</v>
-      </c>
-      <c r="K16" s="30">
-        <v>0</v>
-      </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="N16" s="32">
+      <c r="H16" s="40">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" s="28">
         <f>C16</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:L3"/>
+  <mergeCells count="20">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:C10"/>
-    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="F14:F15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
